--- a/4 четверть_11_JavaScript_SequelizeJS+expressJS.xlsx
+++ b/4 четверть_11_JavaScript_SequelizeJS+expressJS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC8717-2B08-4F84-A6C0-7149479C4C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E040B9D-4122-4500-A890-8D84AC01D23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sequelizeJS DataTypes" sheetId="14" r:id="rId1"/>
@@ -24,12 +24,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="721">
   <si>
     <t>Часть 1</t>
   </si>
@@ -2065,9 +2068,6 @@
 // Now the name was updated to "Ada" in the database!</t>
   </si>
   <si>
-    <t>update…</t>
-  </si>
-  <si>
     <t>`https://sequelize.org/docs/v6/core-concepts/model-instances/#updating-an-instance</t>
   </si>
   <si>
@@ -2143,9 +2143,6 @@
   </si>
   <si>
     <t>DELETE</t>
-  </si>
-  <si>
-    <t>delete…</t>
   </si>
   <si>
     <t>const jane = await User.create({ name: 'Jane' });
@@ -5765,11 +5762,6 @@
   <si>
     <t>Sequelize supports the standard associations: One-To-One, One-To-Many and Many-To-Many.
 To do this, Sequelize provides four types of associations that should be combined to create them:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">const A = sequelize.define('A' /* ... */);
-const B = sequelize.define('B' /* ... */);
-</t>
   </si>
   <si>
     <t>A.hasOne(B); // A HasOne B</t>
@@ -8623,17 +8615,189 @@
   <si>
     <t>RequestLogRepository</t>
   </si>
+  <si>
+    <t>Шаг 1</t>
+  </si>
+  <si>
+    <t>Шаг 2</t>
+  </si>
+  <si>
+    <t>const sequelize = new Sequelize(
+            msconnect.database, 
+            msconnect.user,
+            msconnect.password,
+            {
+                host: msconnect.server,
+                dialect: 'mssql',
+                port: 1433, // стандартный порт SQL Server
+                dialectOptions: {
+                    options: {
+                        encrypt: false, // для локальных БД
+                        trustServerCertificate: true // для разработки
+                    }
+                }
+            }
+            // {
+            //   dialect: 'sqlite',
+            //   storage: '/c/Users/AlexServHW/Desktop/DB/testdatabase.db',
+            //   dialectOptions:{
+            //     mode: SQLite.OPEN_READWRITE | SQLite.OPEN_CREATE | SQLite.OPEN_FULLMUTEX,
+            //   }
+            // }
+        )</t>
+  </si>
+  <si>
+    <t>let SqlConnectionMiddleware = require('../database/SqlConnectionMiddleware');
+const { DataTypes } = require('sequelize');
+const UserAuth = SqlConnectionMiddleware.sequelizeInst.define('user_Auth', {
+    id: {
+      primaryKey: true,
+      type: DataTypes.UUID,
+      allowNull: false,
+      unique: true,
+      defaultValue: DataTypes.UUIDV1,
+        field: 'UserId',
+    },
+    user_ip: {
+      type: DataTypes.STRING,
+      allowNull: false,
+        field: 'UserIp',
+    },
+    user_token: {
+      type: DataTypes.STRING,
+      allowNull: false,
+        field: 'UserToken',
+    },
+}, {
+    tableName: 'user_Auth',
+    timestamps: true,
+});
+(async () =&gt; {
+    await UserAuth.sync({ force: false,  alter: false});
+    console.log('The table for the UserAuth model was just synced (or created, if never existed)!');
+})();
+module.exports = UserAuth;</t>
+  </si>
+  <si>
+    <r>
+      <t>let SqlConnectionMiddleware = require('../database/SqlConnectionMiddleware');
+const { DataTypes } = require('sequelize');
+const UserAuth = SqlConnectionMiddleware.sequelizeInst.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('user_Auth', {
+    id: {
+      primaryKey: true,
+      type: DataTypes.UUID,
+      allowNull: false,
+      unique: true,
+      defaultValue: DataTypes.UUIDV1,
+        field: 'UserId',
+    },
+    user_ip: {
+      type: DataTypes.STRING,
+      allowNull: false,
+        field: 'UserIp',
+    },
+    user_token: {
+      type: DataTypes.STRING,
+      allowNull: false,
+        field: 'UserToken',
+    },
+}, {
+    tableName: 'user_Auth',
+    timestamps: true,
+});
+(async () =&gt; {
+    await UserAuth.sync({ force: false,  alter: false});
+    console.log('The table for the UserAuth model was just synced (or created, if never existed)!');
+})();
+module.exports = UserAuth;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>const A = sequelize.define('A' /* ... */);
+const B = sequelize.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">('B' /* ... */);
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Реальный пример</t>
+  </si>
+  <si>
+    <t>destroy</t>
+  </si>
+  <si>
+    <t>save</t>
+  </si>
+  <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>update (set + save)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9018,20 +9182,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9040,55 +9204,55 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -9100,7 +9264,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -9112,120 +9276,120 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10359,7 +10523,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="63" t="s">
         <v>142</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -10444,7 +10608,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P22" s="1"/>
       <c r="U22" s="1"/>
@@ -10477,13 +10641,19 @@
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="D25" s="10" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B26" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>36</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
@@ -10503,7 +10673,7 @@
       <c r="B29" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="72" t="s">
         <v>191</v>
       </c>
     </row>
@@ -10532,7 +10702,7 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>189</v>
@@ -10554,7 +10724,7 @@
     </row>
     <row r="34" spans="1:21" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B34" s="24" t="s">
         <v>168</v>
@@ -10565,7 +10735,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B35" s="24" t="s">
         <v>169</v>
@@ -10576,7 +10746,7 @@
     </row>
     <row r="36" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B36" s="24" t="s">
         <v>170</v>
@@ -10598,7 +10768,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>177</v>
@@ -10609,7 +10779,7 @@
     </row>
     <row r="39" spans="1:21" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B39" s="21" t="s">
         <v>172</v>
@@ -10620,7 +10790,7 @@
     </row>
     <row r="40" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B40" s="21" t="s">
         <v>176</v>
@@ -10631,7 +10801,7 @@
     </row>
     <row r="41" spans="1:21" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>175</v>
@@ -10682,7 +10852,7 @@
     </row>
     <row r="46" spans="1:21" ht="72" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>186</v>
@@ -10693,7 +10863,7 @@
     </row>
     <row r="47" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>190</v>
@@ -10727,7 +10897,7 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P49" s="1"/>
       <c r="U49" s="1"/>
@@ -10803,7 +10973,7 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="15" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P57" s="1"/>
       <c r="U57" s="1"/>
@@ -10924,7 +11094,7 @@
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P72" s="1"/>
       <c r="U72" s="1"/>
@@ -10932,102 +11102,102 @@
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B73" s="43" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A74" s="49" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C74" s="49" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B75" s="39" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A76" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="C76" s="49" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A77" s="49" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C77" s="49" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="50" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C78" s="12"/>
       <c r="D78" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A79" s="49" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="50" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C80" s="12"/>
       <c r="D80" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="B81" s="49" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.3">
@@ -11055,7 +11225,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P83" s="1"/>
       <c r="U83" s="1"/>
@@ -11063,143 +11233,143 @@
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A84" s="50" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C84" s="12"/>
       <c r="D84" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A85" s="49" t="s">
+        <v>414</v>
+      </c>
+      <c r="B85" s="49" t="s">
+        <v>415</v>
+      </c>
+      <c r="C85" s="49" t="s">
         <v>416</v>
-      </c>
-      <c r="B85" s="49" t="s">
-        <v>417</v>
-      </c>
-      <c r="C85" s="49" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A86" s="50" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C86" s="12"/>
     </row>
     <row r="87" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A87" s="49" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="88" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="49" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A89" s="50" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B89" s="39" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C89" s="12"/>
     </row>
     <row r="90" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A90" s="49" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B90" s="49"/>
       <c r="C90" s="49" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="B91" s="51" t="s">
+        <v>437</v>
+      </c>
+      <c r="C91" s="49" t="s">
         <v>439</v>
-      </c>
-      <c r="C91" s="49" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A92" s="12"/>
       <c r="C92" s="49" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="93" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="12"/>
       <c r="B93" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C93" s="49" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A94" s="12"/>
       <c r="B94" s="1"/>
       <c r="C94" s="49" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A95" s="49" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C95" s="49" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A96" s="12"/>
       <c r="B96" s="49"/>
       <c r="C96" s="49" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="97" spans="1:22" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="C97" s="49" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="50" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C98" s="12"/>
     </row>
     <row r="99" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A99" s="12"/>
       <c r="B99" s="49" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C99" s="49" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.3">
@@ -11419,22 +11589,22 @@
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A121" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B121" s="43" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C121" s="20"/>
     </row>
     <row r="122" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A122" s="49" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C122" s="49" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.3">
@@ -11442,7 +11612,7 @@
         <v>205</v>
       </c>
       <c r="B123" s="39" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
@@ -11504,24 +11674,24 @@
     </row>
     <row r="131" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A131" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B131" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C131" s="20" t="s">
         <v>230</v>
-      </c>
-      <c r="C131" s="20" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="10" t="s">
-        <v>214</v>
+        <v>718</v>
       </c>
       <c r="B132" s="40" t="s">
         <v>212</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="133" spans="1:21" ht="86.4" x14ac:dyDescent="0.3">
@@ -11529,90 +11699,96 @@
         <v>95</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C133" s="20" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A134" s="17" t="s">
+        <v>720</v>
+      </c>
       <c r="B134" s="40" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="135" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C135" s="20" t="s">
-        <v>220</v>
+      <c r="C135" s="72" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A136" s="17" t="s">
+        <v>719</v>
+      </c>
       <c r="B136" s="40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="137" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B137" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C137" s="20" t="s">
-        <v>218</v>
+        <v>215</v>
+      </c>
+      <c r="C137" s="72" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138" s="10" t="s">
-        <v>222</v>
+        <v>717</v>
       </c>
       <c r="B138" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="139" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B139" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C139" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
+      </c>
+      <c r="C139" s="72" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="142" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="143" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C143" s="20" t="s">
         <v>239</v>
-      </c>
-      <c r="C143" s="20" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.3">
@@ -11636,13 +11812,13 @@
     </row>
     <row r="145" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="C145" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P145" s="1"/>
       <c r="U145" s="1"/>
@@ -11650,524 +11826,524 @@
     </row>
     <row r="146" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B146" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="C146" s="20" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A147" s="10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B147" s="39" t="s">
         <v>196</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="148" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B148" s="45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C148" s="45" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="149" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="B149" s="45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A150" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B150" s="39" t="s">
         <v>196</v>
       </c>
       <c r="C150" s="20"/>
       <c r="D150" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="151" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C151" s="45" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C152" s="45" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="153" spans="1:22" ht="230.4" x14ac:dyDescent="0.3">
       <c r="B153" s="45" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C153" s="45" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="154" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="B154" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C154" s="45" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="156" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C156" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B157" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="158" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C158" s="20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="159" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C159" s="20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="160" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C160" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C161" s="20" t="s">
         <v>262</v>
-      </c>
-      <c r="C161" s="20" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C162" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B163" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C163" s="20"/>
       <c r="D163" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C164" s="45" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C165" s="20"/>
       <c r="D165" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B166" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C166" s="45" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B167" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C167" s="20"/>
       <c r="D167" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B168" s="45" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C168" s="45" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D168" s="45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B169" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="B170" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C170" s="45" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D170" s="45" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B171" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C171" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B172" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C172" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C172" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B173" s="46" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C173" s="45"/>
       <c r="D173" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="B174" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C174" s="45" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B175" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C175" s="45" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B176" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C176" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B177" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C177" s="45" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B178" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C178" s="45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C179" s="45" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C180" s="45" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C181" s="45" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C182" s="45" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="19" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C183" s="45"/>
     </row>
     <row r="184" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B184" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C184" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="288" x14ac:dyDescent="0.3">
       <c r="B185" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C185" s="45" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C186" s="45"/>
     </row>
     <row r="187" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="C187" s="45" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B188" s="47" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C188" s="45"/>
       <c r="D188" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
       <c r="B189" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C189" s="45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B190" s="47" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C190" s="45"/>
       <c r="D190" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B191" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C191" s="45" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B192" s="47" t="s">
+        <v>346</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="193" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B193" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C193" s="45" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B194" s="47" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C194" s="45"/>
       <c r="D194" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="195" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C195" s="45" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A197" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B197" s="40" t="s">
         <v>212</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="C198" s="45" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B199" s="47" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="200" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C200" s="45" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A201" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B201" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="202" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C202" s="45" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="203" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C203" s="45" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="204" spans="1:22" x14ac:dyDescent="0.3">
@@ -12191,13 +12367,13 @@
     </row>
     <row r="205" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="P205" s="1"/>
       <c r="U205" s="1"/>
@@ -12205,10 +12381,10 @@
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A206" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B206" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C206" s="2"/>
       <c r="P206" s="1"/>
@@ -12217,33 +12393,33 @@
     </row>
     <row r="207" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C207" s="49" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="208" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C208" s="49" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="C209" s="49" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="331.2" x14ac:dyDescent="0.3">
       <c r="B210" s="49" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C210" s="49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="50" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B211" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C211" s="50" t="s">
         <v>95</v>
@@ -12254,32 +12430,32 @@
     </row>
     <row r="212" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B212" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C212" s="49" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D212" s="49" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B213" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C213" s="49" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B214" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C214" s="50" t="s">
         <v>95</v>
@@ -12290,61 +12466,61 @@
     </row>
     <row r="215" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C215" s="49" t="s">
+        <v>459</v>
+      </c>
+      <c r="D215" s="49" t="s">
         <v>460</v>
-      </c>
-      <c r="C215" s="49" t="s">
-        <v>461</v>
-      </c>
-      <c r="D215" s="49" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D216" s="49" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D217" s="49" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B218" s="43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C218" s="50" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B219" s="49" t="s">
+        <v>463</v>
+      </c>
+      <c r="C219" s="49" t="s">
+        <v>468</v>
+      </c>
+      <c r="D219" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B219" s="49" t="s">
-        <v>465</v>
-      </c>
-      <c r="C219" s="49" t="s">
-        <v>470</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>471</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -12357,7 +12533,7 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -12413,413 +12589,421 @@
         <v>158</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:22" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="49" t="s">
+        <v>483</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="71" t="s">
+        <v>710</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="71" t="s">
+        <v>712</v>
+      </c>
+      <c r="D4" s="33"/>
+    </row>
+    <row r="5" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="71" t="s">
+        <v>711</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>478</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>715</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>475</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>533</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>476</v>
+      </c>
+      <c r="D7" s="54" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>532</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>477</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>531</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>500</v>
+      </c>
+      <c r="D9" s="33"/>
+    </row>
+    <row r="10" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="52" t="s">
+        <v>536</v>
+      </c>
+      <c r="B10" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>534</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="52"/>
+      <c r="B11" s="53" t="s">
+        <v>501</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>535</v>
+      </c>
+      <c r="D11" s="33"/>
+    </row>
+    <row r="12" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="59" t="s">
+        <v>502</v>
+      </c>
+      <c r="B12" s="53" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="53"/>
+      <c r="D12" s="60" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="52" t="s">
+        <v>512</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>505</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>504</v>
+      </c>
+      <c r="D13" s="33"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="52" t="s">
+        <v>509</v>
+      </c>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53" t="s">
+        <v>508</v>
+      </c>
+      <c r="D14" s="33"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="52" t="s">
+        <v>510</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53" t="s">
+        <v>507</v>
+      </c>
+      <c r="D15" s="33"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="52" t="s">
+        <v>511</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53" t="s">
+        <v>506</v>
+      </c>
+      <c r="D16" s="33"/>
+    </row>
+    <row r="17" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="33"/>
+    </row>
+    <row r="18" spans="1:22" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="56"/>
+      <c r="B18" s="57" t="s">
+        <v>514</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>513</v>
+      </c>
+      <c r="D18" s="37"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="58" t="s">
+        <v>485</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="B20" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="58" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="49" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="52" t="s">
-        <v>481</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>477</v>
-      </c>
-      <c r="D4" s="29"/>
-    </row>
-    <row r="5" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
-        <v>541</v>
-      </c>
-      <c r="B5" s="54" t="s">
-        <v>502</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>478</v>
-      </c>
-      <c r="D5" s="55" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
-        <v>541</v>
-      </c>
-      <c r="B6" s="64" t="s">
-        <v>536</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="53" t="s">
-        <v>540</v>
-      </c>
-      <c r="B7" s="64" t="s">
-        <v>535</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>480</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
-        <v>540</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>534</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>503</v>
-      </c>
-      <c r="D8" s="33"/>
-    </row>
-    <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="53" t="s">
-        <v>539</v>
-      </c>
-      <c r="B9" s="54" t="s">
+      <c r="B21" s="58"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="58" t="s">
+        <v>487</v>
+      </c>
+      <c r="B23" s="58"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="61"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="58" t="s">
+        <v>488</v>
+      </c>
+      <c r="B25" s="58"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="49" t="s">
+        <v>498</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="54" t="s">
-        <v>537</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54" t="s">
-        <v>504</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>538</v>
-      </c>
-      <c r="D10" s="33"/>
-    </row>
-    <row r="11" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="60" t="s">
-        <v>505</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>485</v>
-      </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="61" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="53" t="s">
-        <v>515</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>508</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>507</v>
-      </c>
-      <c r="D12" s="33"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="53" t="s">
-        <v>512</v>
-      </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54" t="s">
-        <v>511</v>
-      </c>
-      <c r="D13" s="33"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="53" t="s">
-        <v>513</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54" t="s">
-        <v>510</v>
-      </c>
-      <c r="D14" s="33"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
-        <v>514</v>
-      </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54" t="s">
-        <v>509</v>
-      </c>
-      <c r="D15" s="33"/>
-    </row>
-    <row r="16" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
-        <v>518</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="33"/>
-    </row>
-    <row r="17" spans="1:22" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" s="58" t="s">
+      <c r="D28" s="50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49" t="s">
+        <v>495</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="U30" s="5"/>
+    </row>
+    <row r="31" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C31" s="15" t="s">
         <v>516</v>
       </c>
-      <c r="D17" s="37"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="59" t="s">
-        <v>488</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
-        <v>495</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="59" t="s">
-        <v>489</v>
-      </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="62"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
-        <v>490</v>
-      </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-    </row>
-    <row r="23" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A24" s="59" t="s">
-        <v>491</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="49" t="s">
-        <v>501</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="50" t="s">
-        <v>499</v>
-      </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49" t="s">
-        <v>498</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="U29" s="5"/>
-    </row>
-    <row r="30" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C30" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="P30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="2"/>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="B31" s="1"/>
-      <c r="C31" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>523</v>
+      </c>
       <c r="P31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="2"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" s="50" t="s">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="P32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="2"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="50" t="s">
+        <v>517</v>
+      </c>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="49" t="s">
+        <v>519</v>
+      </c>
+      <c r="B34" s="49" t="s">
         <v>520</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="49"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="49" t="s">
-        <v>522</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>523</v>
-      </c>
-      <c r="C33" s="49" t="s">
+      <c r="C34" s="49" t="s">
+        <v>525</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="50" t="s">
+        <v>518</v>
+      </c>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="12"/>
+      <c r="B36" s="49" t="s">
+        <v>521</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>526</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="12"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="U38" s="5"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C39" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="P39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="2"/>
+    </row>
+    <row r="40" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="50" t="s">
+        <v>529</v>
+      </c>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="12"/>
+      <c r="B41" s="49" t="s">
         <v>528</v>
       </c>
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A34" s="50" t="s">
-        <v>521</v>
-      </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="49" t="s">
-        <v>524</v>
-      </c>
-      <c r="C35" s="49" t="s">
-        <v>529</v>
-      </c>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="U37" s="5"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C38" s="15" t="s">
+      <c r="C41" s="49" t="s">
         <v>527</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="P38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="2"/>
-    </row>
-    <row r="39" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="50" t="s">
-        <v>532</v>
-      </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49"/>
-      <c r="D39" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="49" t="s">
-        <v>531</v>
-      </c>
-      <c r="C40" s="49" t="s">
-        <v>530</v>
-      </c>
-      <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.3">
@@ -12829,151 +13013,157 @@
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="U43" s="5"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C44" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="P44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="2"/>
-    </row>
-    <row r="45" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="50" t="s">
-        <v>552</v>
-      </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="2" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="U44" s="5"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C45" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="P45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="2"/>
+    </row>
+    <row r="46" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="50" t="s">
+        <v>549</v>
+      </c>
       <c r="B46" s="49"/>
-      <c r="C46" s="49" t="s">
-        <v>547</v>
-      </c>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+      <c r="C46" s="49"/>
+      <c r="D46" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="12"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="C47" s="49" t="s">
-        <v>550</v>
-      </c>
+      <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C48" s="49" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C50" s="49" t="s">
         <v>545</v>
       </c>
-      <c r="C48" s="49" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="C50" s="49"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="C51" s="49" t="s">
-        <v>563</v>
-      </c>
+      <c r="A51" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="C51" s="49"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="C61" s="49" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D62" s="1" t="s">
-        <v>567</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="C62" s="49" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D63" s="1" t="s">
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -13042,10 +13232,10 @@
     </row>
     <row r="2" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C2" s="15" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="P2" s="1"/>
       <c r="U2" s="1"/>
@@ -13053,121 +13243,121 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="67"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C4" s="66" t="s">
-        <v>571</v>
+      <c r="C4" s="64" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C5" s="66" t="s">
-        <v>575</v>
+        <v>571</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>589</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="B7" s="64" t="s">
         <v>588</v>
       </c>
-      <c r="C6" s="66" t="s">
-        <v>592</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="B7" s="66" t="s">
-        <v>591</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>587</v>
+      <c r="C7" s="64" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B8" s="14"/>
-      <c r="C8" s="67"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C9" s="66" t="s">
-        <v>572</v>
+      <c r="C9" s="64" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>577</v>
+        <v>573</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>589</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="B12" s="64" t="s">
         <v>588</v>
       </c>
-      <c r="C11" s="66" t="s">
-        <v>592</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="B12" s="66" t="s">
-        <v>591</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>590</v>
+      <c r="C12" s="64" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="C15" s="66" t="s">
-        <v>580</v>
+      <c r="C15" s="64" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>582</v>
+        <v>580</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>586</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>585</v>
+        <v>581</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="64" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -13295,7 +13485,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C9" s="2"/>
       <c r="P9" s="1"/>
@@ -13304,20 +13494,20 @@
     </row>
     <row r="10" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C10" s="2"/>
       <c r="F10" s="1" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>612</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="P10" s="1"/>
       <c r="U10" s="1"/>
@@ -13334,7 +13524,7 @@
     </row>
     <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="C12" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="P12" s="1"/>
       <c r="U12" s="1"/>
@@ -13342,31 +13532,31 @@
     </row>
     <row r="13" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="C13" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="P13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="71" t="s">
-        <v>613</v>
-      </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72" t="s">
-        <v>614</v>
-      </c>
-      <c r="D14" s="70"/>
+      <c r="A14" s="69" t="s">
+        <v>610</v>
+      </c>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70" t="s">
+        <v>611</v>
+      </c>
+      <c r="D14" s="68"/>
       <c r="P14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="2"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C15" s="2"/>
       <c r="P15" s="1"/>
@@ -13375,7 +13565,7 @@
     </row>
     <row r="16" spans="1:22" ht="403.2" x14ac:dyDescent="0.3">
       <c r="C16" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="P16" s="1"/>
       <c r="U16" s="1"/>
@@ -13383,459 +13573,459 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="66" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="288" x14ac:dyDescent="0.3">
+      <c r="C19" s="67" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="C20" s="67" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="C21" s="67" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="288" x14ac:dyDescent="0.3">
-      <c r="C19" s="69" t="s">
+    <row r="22" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C22" s="67" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="C20" s="69" t="s">
+    <row r="23" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="C23" s="67" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="C24" s="67" t="s">
         <v>600</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="C21" s="69" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C22" s="69" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="C23" s="69" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="C24" s="69" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="C26" s="69" t="s">
-        <v>605</v>
+      <c r="C26" s="67" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
+        <v>614</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="67" t="s">
         <v>615</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="69" t="s">
+      <c r="C29" s="67" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A30" s="67" t="s">
         <v>617</v>
       </c>
-      <c r="C28" s="69" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="69" t="s">
+      <c r="C30" s="67" t="s">
         <v>618</v>
       </c>
-      <c r="C29" s="69" t="s">
+    </row>
+    <row r="31" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A31" s="67" t="s">
+        <v>620</v>
+      </c>
+      <c r="C31" s="67" t="s">
         <v>619</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="A30" s="69" t="s">
-        <v>620</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="A31" s="69" t="s">
-        <v>623</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C33" s="69" t="s">
-        <v>630</v>
+        <v>636</v>
+      </c>
+      <c r="C33" s="67" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C34" s="69" t="s">
-        <v>631</v>
+        <v>632</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C35" s="69" t="s">
         <v>633</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="C36" s="69" t="s">
         <v>634</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C37" s="69" t="s">
-        <v>632</v>
+        <v>635</v>
+      </c>
+      <c r="C37" s="67" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="C38" s="69" t="s">
-        <v>640</v>
+        <v>638</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C41" s="69" t="s">
-        <v>642</v>
+        <v>644</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C42" s="69" t="s">
-        <v>643</v>
+        <v>632</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C43" s="69" t="s">
-        <v>644</v>
+        <v>646</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C44" s="69" t="s">
-        <v>645</v>
+        <v>647</v>
+      </c>
+      <c r="C44" s="67" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C45" s="69" t="s">
-        <v>646</v>
+        <v>648</v>
+      </c>
+      <c r="C45" s="67" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C46" s="69" t="s">
-        <v>652</v>
+        <v>650</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C47" s="1"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="67" t="s">
+        <v>659</v>
+      </c>
+      <c r="C49" s="67" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A50" s="67" t="s">
+        <v>656</v>
+      </c>
+      <c r="C50" s="67" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="67" t="s">
+        <v>657</v>
+      </c>
+      <c r="C51" s="67" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="67" t="s">
         <v>658</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="69" t="s">
-        <v>662</v>
-      </c>
-      <c r="C49" s="69" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="A50" s="69" t="s">
-        <v>659</v>
-      </c>
-      <c r="C50" s="69" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="69" t="s">
-        <v>660</v>
-      </c>
-      <c r="C51" s="69" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="69" t="s">
-        <v>661</v>
-      </c>
-      <c r="C52" s="69" t="s">
-        <v>657</v>
+      <c r="C52" s="67" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="C53" s="69" t="s">
-        <v>665</v>
+        <v>663</v>
+      </c>
+      <c r="C53" s="67" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C55" s="69" t="s">
-        <v>668</v>
+        <v>669</v>
+      </c>
+      <c r="C55" s="67" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="C56" s="69" t="s">
-        <v>670</v>
+        <v>668</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="C58" s="69" t="s">
-        <v>675</v>
+        <v>681</v>
+      </c>
+      <c r="C58" s="67" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C59" s="69" t="s">
-        <v>676</v>
+        <v>677</v>
+      </c>
+      <c r="C59" s="67" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="C60" s="69" t="s">
         <v>678</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="C61" s="69" t="s">
         <v>679</v>
+      </c>
+      <c r="C61" s="67" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="C62" s="69" t="s">
-        <v>677</v>
+        <v>680</v>
+      </c>
+      <c r="C62" s="67" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C63" s="69" t="s">
-        <v>685</v>
+        <v>683</v>
+      </c>
+      <c r="C63" s="67" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="69"/>
+      <c r="C64" s="67"/>
     </row>
     <row r="65" spans="1:3" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="C65" s="69" t="s">
         <v>706</v>
+      </c>
+      <c r="C65" s="67" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="C66" s="69" t="s">
-        <v>707</v>
+        <v>666</v>
+      </c>
+      <c r="C66" s="67" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="C67" s="69" t="s">
-        <v>708</v>
+        <v>622</v>
+      </c>
+      <c r="C67" s="67" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C69" s="69" t="s">
-        <v>688</v>
+        <v>686</v>
+      </c>
+      <c r="C69" s="67" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C70" s="69" t="s">
-        <v>690</v>
+        <v>688</v>
+      </c>
+      <c r="C70" s="67" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C71" s="69" t="s">
-        <v>692</v>
+        <v>690</v>
+      </c>
+      <c r="C71" s="67" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="C72" s="69" t="s">
-        <v>694</v>
+        <v>692</v>
+      </c>
+      <c r="C72" s="67" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="C73" s="69" t="s">
-        <v>696</v>
+        <v>694</v>
+      </c>
+      <c r="C73" s="67" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="C74" s="69" t="s">
-        <v>698</v>
+        <v>696</v>
+      </c>
+      <c r="C74" s="67" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="C75" s="69" t="s">
-        <v>700</v>
+        <v>698</v>
+      </c>
+      <c r="C75" s="67" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="C76" s="69" t="s">
-        <v>702</v>
+        <v>700</v>
+      </c>
+      <c r="C76" s="67" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
